--- a/docs/downloads/20260828_Ukay_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/20260828_Ukay_Teduh_Weekly_Update.xlsx
@@ -609,7 +609,7 @@
         <v/>
       </c>
       <c r="I5" s="11" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J5" s="12">
         <f>I5/$D$5</f>
@@ -617,7 +617,7 @@
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>Latest sales - Block A: 54 units, Block B: 41 units</t>
+          <t>Latest sales - Block A: 54 units, Block B: 40 units</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
         <v/>
       </c>
       <c r="I6" s="11" t="n">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="J6" s="12">
         <f>I6/$D$6</f>
@@ -659,7 +659,7 @@
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>Latest sales - Block A1: 45 units, Block A2: 201 units, Block B: 97 units</t>
+          <t>Latest sales - Block A1: 45 units, Block A2: 202 units, Block B: 100 units</t>
         </is>
       </c>
     </row>
